--- a/templates/STUDENT INFO REGISTRATION.xlsx
+++ b/templates/STUDENT INFO REGISTRATION.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.1.118\Webservices\clap.ins\WebCWS\portal-handler\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7188"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -440,7 +440,7 @@
   <dimension ref="A1:H1"/>
   <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.21875" style="2"/>
     <col min="2" max="2" width="21.44140625" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.77734375" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="79.77734375" style="3" customWidth="1"/>
